--- a/results/pvdaq_1278/report.xlsx
+++ b/results/pvdaq_1278/report.xlsx
@@ -5381,9 +5381,7 @@
       <c r="J2" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="K2" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="K2" s="6" t="n"/>
       <c r="L2" s="6" t="n"/>
     </row>
     <row r="3">
@@ -5487,7 +5485,7 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.9945653199849828</v>
+        <v>0.9945653199849829</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>0.98</v>
